--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-organization.xlsx
@@ -804,7 +804,7 @@
     <t>福祉医療施設を区別するため医療機関コード（１０桁）を格納するためのIdentifier/Slicing定義。</t>
   </si>
   <si>
-    <t xml:space="preserve">systemはFixed Valueの```http://jpfhir.jp/fhir/core/IdSystem/medicalInstitutionCode```を使用する。  
+    <t xml:space="preserve">systemはFixed Valueの```http://jpfhir.jp/fhir/core/IdSystem/insurance-medical-institution-no```を使用する。  
 value : ```医療機関コード（１０桁）```を使用する。  
 医療機関コード（１０桁）の詳細はOrganizationプロファイルの医療機関コード１０桁の説明を参照すること。 </t>
   </si>
@@ -827,7 +827,7 @@
     <t>Organization.identifier:medicalInstitutionCode.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/medicalInstitutionCode</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/insurance-medical-institution-no</t>
   </si>
   <si>
     <t>Organization.identifier:medicalInstitutionCode.value</t>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-organization.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Organization</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Organization|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -364,7 +364,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -455,7 +455,7 @@
     <t>prefectureNo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_PrefectureNo}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_PrefectureNo|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>organizationCategory</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_InsuranceOrganizationCategory}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_InsuranceOrganizationCategory|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -503,7 +503,7 @@
     <t>organizationNo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_InsuranceOrganizationNo}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_InsuranceOrganizationNo|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -679,7 +679,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -767,7 +767,7 @@
     <t>Organization.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -944,7 +944,7 @@
     <t>組織を分類するために使用されます。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1576,7 +1576,7 @@
     <t>「連絡を取りたい目的のための連絡先」となります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>./type</t>
@@ -1585,7 +1585,7 @@
     <t>Organization.contact.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {http://jpfhir.jp/fhir/core/StructureDefinition/JP_HumanName}
+    <t xml:space="preserve">HumanName {http://jpfhir.jp/fhir/core/StructureDefinition/JP_HumanName|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1643,7 +1643,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1970,7 +1970,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="91.34375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="99.3359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-organization.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Organization|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Organization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -364,7 +364,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -455,7 +455,7 @@
     <t>prefectureNo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_PrefectureNo|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_PrefectureNo}
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>organizationCategory</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_InsuranceOrganizationCategory|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_InsuranceOrganizationCategory}
 </t>
   </si>
   <si>
@@ -503,7 +503,7 @@
     <t>organizationNo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_InsuranceOrganizationNo|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Organization_InsuranceOrganizationNo}
 </t>
   </si>
   <si>
@@ -679,7 +679,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -767,7 +767,7 @@
     <t>Organization.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -944,7 +944,7 @@
     <t>組織を分類するために使用されます。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1576,7 +1576,7 @@
     <t>「連絡を取りたい目的のための連絡先」となります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
   </si>
   <si>
     <t>./type</t>
@@ -1585,7 +1585,7 @@
     <t>Organization.contact.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {http://jpfhir.jp/fhir/core/StructureDefinition/JP_HumanName|1.3.0-dev}
+    <t xml:space="preserve">HumanName {http://jpfhir.jp/fhir/core/StructureDefinition/JP_HumanName}
 </t>
   </si>
   <si>
@@ -1643,7 +1643,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1)
+    <t xml:space="preserve">Reference(Endpoint)
 </t>
   </si>
   <si>
@@ -1970,7 +1970,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="99.3359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="91.34375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
